--- a/output/pdf_financials_xlsx/BK.xlsx
+++ b/output/pdf_financials_xlsx/BK.xlsx
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>5.272515</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>60.390826</v>
       </c>
     </row>
     <row r="35">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>5.272515</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>60.390826</v>
       </c>
     </row>
     <row r="37">
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>238.514116</v>
+        <v>233.241601</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>353.038148</v>
+        <v>292.647322</v>
       </c>
     </row>
     <row r="49">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">

--- a/output/pdf_financials_xlsx/BK.xlsx
+++ b/output/pdf_financials_xlsx/BK.xlsx
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2.017205</v>
+        <v>2.040788</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2.553634</v>
+        <v>2.575659</v>
       </c>
     </row>
     <row r="8">
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>32.683719</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>9.795559000000001</v>
       </c>
     </row>
     <row r="116">
@@ -2212,15 +2212,11 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>5.774768</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>5.272515</v>
       </c>
     </row>
     <row r="131">
@@ -2255,15 +2251,11 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>5.272515</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>60.390826</v>
       </c>
     </row>
     <row r="134">
@@ -3040,7 +3032,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>32.683719</v>
       </c>
@@ -3350,7 +3346,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>5.774768</v>
       </c>
@@ -3374,7 +3374,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
         <v>5.272515</v>
       </c>
@@ -4610,7 +4614,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E93" s="5" t="n">
         <v>0.023583</v>
       </c>
@@ -4886,7 +4894,11 @@
           <t>Distributions on Preferred shares</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E104" s="5" t="n">
         <v>-5.256524</v>
       </c>
